--- a/data/numeric/input/data_222/人员名单.xlsx
+++ b/data/numeric/input/data_222/人员名单.xlsx
@@ -2940,18 +2940,26 @@
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
+  <documentManagement>
+    <SharedWithUsers xmlns="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{83A35898-7F1C-4445-9219-4DAE646015EE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{98A51703-5CE4-43FE-9A87-AB378EA83608}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DDEAFA90-3222-4864-8BB1-1A50217EA3F4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E65E6B78-A2EC-4FB8-8462-B6906976AF2A}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C96FFE9E-8DD9-4AB9-A564-F031897D3DC5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F8DF974F-2C78-4BB4-9A30-D61B510271E1}"/>
 </file>